--- a/db/A7XLK-1111-HouseApp4.xlsx
+++ b/db/A7XLK-1111-HouseApp4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D8DCFF-816D-0A4C-8DE5-C7301B85A665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F6EC31-0DF0-174C-B6BD-833BB3C0E4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-5500" yWindow="-20620" windowWidth="27320" windowHeight="16380" xr2:uid="{33D194D6-A429-7949-A97B-0894189945E2}"/>
   </bookViews>
@@ -5234,7 +5234,7 @@
         <v>752</v>
       </c>
       <c r="D2" s="12" t="str">
-        <f>CONCATENATE(A2," ",C2)</f>
+        <f t="shared" ref="D2:D25" si="0">CONCATENATE(A2," ",C2)</f>
         <v>511 遠雄文青</v>
       </c>
       <c r="E2" s="12" t="s">
@@ -5266,11 +5266,11 @@
         <v>15</v>
       </c>
       <c r="O2" s="15">
-        <f>(M2+N2)/2</f>
+        <f t="shared" ref="O2:O16" si="1">(M2+N2)/2</f>
         <v>15</v>
       </c>
       <c r="P2" s="15">
-        <f>N2-O2</f>
+        <f t="shared" ref="P2:P16" si="2">N2-O2</f>
         <v>0</v>
       </c>
       <c r="Q2" s="9" t="s">
@@ -5283,11 +5283,11 @@
         <v>15</v>
       </c>
       <c r="T2" s="15">
-        <f>S2-R2</f>
+        <f t="shared" ref="T2:T16" si="3">S2-R2</f>
         <v>0</v>
       </c>
       <c r="U2" s="15">
-        <f>(R2+S2)/2</f>
+        <f t="shared" ref="U2:U25" si="4">(R2+S2)/2</f>
         <v>15</v>
       </c>
       <c r="V2" s="15" t="s">
@@ -5368,7 +5368,7 @@
         <v>761</v>
       </c>
       <c r="D3" s="12" t="str">
-        <f>CONCATENATE(A3," ",C3)</f>
+        <f t="shared" si="0"/>
         <v>512 皇翔歡喜城</v>
       </c>
       <c r="E3" s="12" t="s">
@@ -5400,11 +5400,11 @@
         <v>15</v>
       </c>
       <c r="O3" s="15">
-        <f>(M3+N3)/2</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="P3" s="15">
-        <f>N3-O3</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q3" s="9" t="s">
@@ -5417,11 +5417,11 @@
         <v>15</v>
       </c>
       <c r="T3" s="15">
-        <f>S3-R3</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U3" s="15">
-        <f>(R3+S3)/2</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="V3" s="15" t="s">
@@ -5499,7 +5499,7 @@
         <v>769</v>
       </c>
       <c r="D4" s="12" t="str">
-        <f>CONCATENATE(A4," ",C4)</f>
+        <f t="shared" si="0"/>
         <v>513 名軒快樂家</v>
       </c>
       <c r="E4" s="12" t="s">
@@ -5531,11 +5531,11 @@
         <v>15</v>
       </c>
       <c r="O4" s="15">
-        <f>(M4+N4)/2</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="P4" s="15">
-        <f>N4-O4</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q4" s="9" t="s">
@@ -5548,11 +5548,11 @@
         <v>15</v>
       </c>
       <c r="T4" s="15">
-        <f>S4-R4</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U4" s="15">
-        <f>(R4+S4)/2</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="V4" s="15" t="s">
@@ -5630,7 +5630,7 @@
         <v>777</v>
       </c>
       <c r="D5" s="12" t="str">
-        <f>CONCATENATE(A5," ",C5)</f>
+        <f t="shared" si="0"/>
         <v>514 麗寶快樂家</v>
       </c>
       <c r="E5" s="12" t="s">
@@ -5662,11 +5662,11 @@
         <v>15</v>
       </c>
       <c r="O5" s="15">
-        <f>(M5+N5)/2</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="P5" s="15">
-        <f>N5-O5</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q5" s="9" t="s">
@@ -5679,11 +5679,11 @@
         <v>15</v>
       </c>
       <c r="T5" s="15">
-        <f>S5-R5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U5" s="15">
-        <f>(R5+S5)/2</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="V5" s="15" t="s">
@@ -5761,7 +5761,7 @@
         <v>785</v>
       </c>
       <c r="D6" s="12" t="str">
-        <f>CONCATENATE(A6," ",C6)</f>
+        <f t="shared" si="0"/>
         <v>308 合遠新天地</v>
       </c>
       <c r="E6" s="9" t="s">
@@ -5787,11 +5787,11 @@
         <v>26</v>
       </c>
       <c r="O6" s="15">
-        <f>(M6+N6)/2</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="P6" s="15">
-        <f>N6-O6</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Q6" s="9" t="s">
@@ -5804,11 +5804,11 @@
         <v>26</v>
       </c>
       <c r="T6" s="15">
-        <f>S6-R6</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="U6" s="15">
-        <f>(R6+S6)/2</f>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="V6" s="15" t="s">
@@ -5964,7 +5964,7 @@
         <v>805</v>
       </c>
       <c r="D7" s="12" t="str">
-        <f>CONCATENATE(A7," ",C7)</f>
+        <f t="shared" si="0"/>
         <v>103 樂捷市</v>
       </c>
       <c r="E7" s="9" t="s">
@@ -5996,11 +5996,11 @@
         <v>26</v>
       </c>
       <c r="O7" s="15">
-        <f>(M7+N7)/2</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="P7" s="15">
-        <f>N7-O7</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q7" s="9" t="s">
@@ -6013,11 +6013,11 @@
         <v>26</v>
       </c>
       <c r="T7" s="15">
-        <f>S7-R7</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U7" s="15">
-        <f>(R7+S7)/2</f>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="V7" s="15" t="s">
@@ -6179,7 +6179,7 @@
         <v>824</v>
       </c>
       <c r="D8" s="12" t="str">
-        <f>CONCATENATE(A8," ",C8)</f>
+        <f t="shared" si="0"/>
         <v>504 竹城宇治</v>
       </c>
       <c r="E8" s="12" t="s">
@@ -6209,11 +6209,11 @@
         <v>30</v>
       </c>
       <c r="O8" s="15">
-        <f>(M8+N8)/2</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="P8" s="15">
-        <f>N8-O8</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q8" s="9" t="s">
@@ -6226,11 +6226,11 @@
         <v>30</v>
       </c>
       <c r="T8" s="15">
-        <f>S8-R8</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U8" s="15">
-        <f>(R8+S8)/2</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="V8" s="15" t="s">
@@ -6380,7 +6380,7 @@
         <v>842</v>
       </c>
       <c r="D9" s="12" t="str">
-        <f>CONCATENATE(A9," ",C9)</f>
+        <f t="shared" si="0"/>
         <v>503 竹城明治</v>
       </c>
       <c r="E9" s="12" t="s">
@@ -6412,11 +6412,11 @@
         <v>30</v>
       </c>
       <c r="O9" s="15">
-        <f>(M9+N9)/2</f>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="P9" s="15">
-        <f>N9-O9</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Q9" s="9" t="s">
@@ -6429,11 +6429,11 @@
         <v>30</v>
       </c>
       <c r="T9" s="15">
-        <f>S9-R9</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="U9" s="15">
-        <f>(R9+S9)/2</f>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="V9" s="15" t="s">
@@ -6580,7 +6580,7 @@
         <v>860</v>
       </c>
       <c r="D10" s="12" t="str">
-        <f>CONCATENATE(A10," ",C10)</f>
+        <f t="shared" si="0"/>
         <v>104 奇幻莊園</v>
       </c>
       <c r="E10" s="12" t="s">
@@ -6610,11 +6610,11 @@
         <v>25.5</v>
       </c>
       <c r="O10" s="15">
-        <f>(M10+N10)/2</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="P10" s="15">
-        <f>N10-O10</f>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="Q10" s="9" t="s">
@@ -6627,11 +6627,11 @@
         <v>25.5</v>
       </c>
       <c r="T10" s="15">
-        <f>S10-R10</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="U10" s="15">
-        <f>(R10+S10)/2</f>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="V10" s="15" t="s">
@@ -6793,7 +6793,7 @@
         <v>883</v>
       </c>
       <c r="D11" s="12" t="str">
-        <f>CONCATENATE(A11," ",C11)</f>
+        <f t="shared" si="0"/>
         <v>203 耀台北</v>
       </c>
       <c r="E11" s="12" t="s">
@@ -6825,11 +6825,11 @@
         <v>28</v>
       </c>
       <c r="O11" s="15">
-        <f>(M11+N11)/2</f>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="P11" s="15">
-        <f>N11-O11</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Q11" s="9" t="s">
@@ -6842,11 +6842,11 @@
         <v>28</v>
       </c>
       <c r="T11" s="15">
-        <f>S11-R11</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="U11" s="15">
-        <f>(R11+S11)/2</f>
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
       <c r="V11" s="15" t="s">
@@ -7002,7 +7002,7 @@
         <v>900</v>
       </c>
       <c r="D12" s="12" t="str">
-        <f>CONCATENATE(A12," ",C12)</f>
+        <f t="shared" si="0"/>
         <v>205 富宇敦峰</v>
       </c>
       <c r="E12" s="12" t="s">
@@ -7034,11 +7034,11 @@
         <v>32</v>
       </c>
       <c r="O12" s="15">
-        <f>(M12+N12)/2</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="P12" s="15">
-        <f>N12-O12</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Q12" s="9" t="s">
@@ -7051,11 +7051,11 @@
         <v>42</v>
       </c>
       <c r="T12" s="15">
-        <f>S12-R12</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="U12" s="15">
-        <f>(R12+S12)/2</f>
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="W12" s="9" t="s">
@@ -7214,7 +7214,7 @@
         <v>921</v>
       </c>
       <c r="D13" s="12" t="str">
-        <f>CONCATENATE(A13," ",C13)</f>
+        <f t="shared" si="0"/>
         <v>304 新潤鉑麗</v>
       </c>
       <c r="E13" s="12" t="s">
@@ -7246,11 +7246,11 @@
         <v>29</v>
       </c>
       <c r="O13" s="15">
-        <f>(M13+N13)/2</f>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="P13" s="15">
-        <f>N13-O13</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Q13" s="9" t="s">
@@ -7263,11 +7263,11 @@
         <v>29</v>
       </c>
       <c r="T13" s="15">
-        <f>S13-R13</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="U13" s="15">
-        <f>(R13+S13)/2</f>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="V13" s="15" t="s">
@@ -7429,7 +7429,7 @@
         <v>942</v>
       </c>
       <c r="D14" s="12" t="str">
-        <f>CONCATENATE(A14," ",C14)</f>
+        <f t="shared" si="0"/>
         <v>305 根津苑</v>
       </c>
       <c r="E14" s="12" t="s">
@@ -7461,11 +7461,11 @@
         <v>26</v>
       </c>
       <c r="O14" s="15">
-        <f>(M14+N14)/2</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="P14" s="15">
-        <f>N14-O14</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Q14" s="9" t="s">
@@ -7478,11 +7478,11 @@
         <v>28</v>
       </c>
       <c r="T14" s="15">
-        <f>S14-R14</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="U14" s="15">
-        <f>(R14+S14)/2</f>
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
       <c r="W14" s="9" t="s">
@@ -7641,7 +7641,7 @@
         <v>959</v>
       </c>
       <c r="D15" s="12" t="str">
-        <f>CONCATENATE(A15," ",C15)</f>
+        <f t="shared" si="0"/>
         <v>402 金捷市</v>
       </c>
       <c r="E15" s="12" t="s">
@@ -7673,11 +7673,11 @@
         <v>30.5</v>
       </c>
       <c r="O15" s="15">
-        <f>(M15+N15)/2</f>
+        <f t="shared" si="1"/>
         <v>30.5</v>
       </c>
       <c r="P15" s="15">
-        <f>N15-O15</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q15" s="9" t="s">
@@ -7690,11 +7690,11 @@
         <v>30.5</v>
       </c>
       <c r="T15" s="15">
-        <f>S15-R15</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U15" s="15">
-        <f>(R15+S15)/2</f>
+        <f t="shared" si="4"/>
         <v>30.5</v>
       </c>
       <c r="W15" s="9" t="s">
@@ -7853,7 +7853,7 @@
         <v>977</v>
       </c>
       <c r="D16" s="12" t="str">
-        <f>CONCATENATE(A16," ",C16)</f>
+        <f t="shared" si="0"/>
         <v>406 富御捷境</v>
       </c>
       <c r="E16" s="12" t="s">
@@ -7885,11 +7885,11 @@
         <v>29</v>
       </c>
       <c r="O16" s="15">
-        <f>(M16+N16)/2</f>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="P16" s="15">
-        <f>N16-O16</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Q16" s="9" t="s">
@@ -7902,11 +7902,11 @@
         <v>32</v>
       </c>
       <c r="T16" s="15">
-        <f>S16-R16</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="U16" s="15">
-        <f>(R16+S16)/2</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="W16" s="9" t="s">
@@ -8065,7 +8065,7 @@
         <v>995</v>
       </c>
       <c r="D17" s="12" t="str">
-        <f>CONCATENATE(A17," ",C17)</f>
+        <f t="shared" si="0"/>
         <v>506 和煦隆陞</v>
       </c>
       <c r="E17" s="12" t="s">
@@ -8091,7 +8091,7 @@
         <v>998</v>
       </c>
       <c r="U17" s="15">
-        <f>(R17+S17)/2</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AD17" s="9" t="s">
@@ -8193,7 +8193,7 @@
         <v>1009</v>
       </c>
       <c r="D18" s="12" t="str">
-        <f>CONCATENATE(A18," ",C18)</f>
+        <f t="shared" si="0"/>
         <v>107 台北國際村</v>
       </c>
       <c r="E18" s="12" t="s">
@@ -8225,11 +8225,11 @@
         <v>26</v>
       </c>
       <c r="O18" s="15">
-        <f>(M18+N18)/2</f>
+        <f t="shared" ref="O18:O25" si="5">(M18+N18)/2</f>
         <v>25.5</v>
       </c>
       <c r="P18" s="15">
-        <f>N18-O18</f>
+        <f t="shared" ref="P18:P25" si="6">N18-O18</f>
         <v>0.5</v>
       </c>
       <c r="Q18" s="9" t="s">
@@ -8242,11 +8242,11 @@
         <v>29</v>
       </c>
       <c r="T18" s="15">
-        <f>S18-R18</f>
+        <f t="shared" ref="T18:T25" si="7">S18-R18</f>
         <v>2</v>
       </c>
       <c r="U18" s="15">
-        <f>(R18+S18)/2</f>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="W18" s="9" t="s">
@@ -8405,7 +8405,7 @@
         <v>1030</v>
       </c>
       <c r="D19" s="12" t="str">
-        <f>CONCATENATE(A19," ",C19)</f>
+        <f t="shared" si="0"/>
         <v>309 友文化</v>
       </c>
       <c r="E19" s="12" t="s">
@@ -8437,11 +8437,11 @@
         <v>31</v>
       </c>
       <c r="O19" s="15">
-        <f>(M19+N19)/2</f>
+        <f t="shared" si="5"/>
         <v>30.5</v>
       </c>
       <c r="P19" s="15">
-        <f>N19-O19</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="Q19" s="9" t="s">
@@ -8454,11 +8454,11 @@
         <v>28</v>
       </c>
       <c r="T19" s="15">
-        <f>S19-R19</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U19" s="15">
-        <f>(R19+S19)/2</f>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="W19" s="9" t="s">
@@ -8617,7 +8617,7 @@
         <v>1047</v>
       </c>
       <c r="D20" s="12" t="str">
-        <f>CONCATENATE(A20," ",C20)</f>
+        <f t="shared" si="0"/>
         <v>106 玉子園</v>
       </c>
       <c r="E20" s="12" t="s">
@@ -8649,11 +8649,11 @@
         <v>28</v>
       </c>
       <c r="O20" s="15">
-        <f>(M20+N20)/2</f>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="P20" s="15">
-        <f>N20-O20</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q20" s="9" t="s">
@@ -8666,11 +8666,11 @@
         <v>28</v>
       </c>
       <c r="T20" s="15">
-        <f>S20-R20</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="U20" s="15">
-        <f>(R20+S20)/2</f>
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
       <c r="V20" s="15" t="s">
@@ -8826,7 +8826,7 @@
         <v>1065</v>
       </c>
       <c r="D21" s="12" t="str">
-        <f>CONCATENATE(A21," ",C21)</f>
+        <f t="shared" si="0"/>
         <v>204 皇普MVP</v>
       </c>
       <c r="E21" s="12" t="s">
@@ -8857,11 +8857,11 @@
         <v>26</v>
       </c>
       <c r="O21" s="15">
-        <f>(M21+N21)/2</f>
+        <f t="shared" si="5"/>
         <v>25.5</v>
       </c>
       <c r="P21" s="15">
-        <f>N21-O21</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="Q21" s="9" t="s">
@@ -8874,11 +8874,11 @@
         <v>28</v>
       </c>
       <c r="T21" s="15">
-        <f>S21-R21</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="U21" s="15">
-        <f>(R21+S21)/2</f>
+        <f t="shared" si="4"/>
         <v>27.5</v>
       </c>
       <c r="W21" s="9" t="s">
@@ -9028,7 +9028,7 @@
         <v>1084</v>
       </c>
       <c r="D22" s="12" t="str">
-        <f>CONCATENATE(A22," ",C22)</f>
+        <f t="shared" si="0"/>
         <v>303 新潤翡麗</v>
       </c>
       <c r="E22" s="12" t="s">
@@ -9060,11 +9060,11 @@
         <v>28</v>
       </c>
       <c r="O22" s="15">
-        <f>(M22+N22)/2</f>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="P22" s="15">
-        <f>N22-O22</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q22" s="9" t="s">
@@ -9077,11 +9077,11 @@
         <v>36</v>
       </c>
       <c r="T22" s="15">
-        <f>S22-R22</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="U22" s="15">
-        <f>(R22+S22)/2</f>
+        <f t="shared" si="4"/>
         <v>34.5</v>
       </c>
       <c r="Z22" s="9" t="s">
@@ -9234,7 +9234,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="12" t="str">
-        <f>CONCATENATE(A23," ",C23)</f>
+        <f t="shared" si="0"/>
         <v>310 水悅青青</v>
       </c>
       <c r="E23" s="12" t="s">
@@ -9266,11 +9266,11 @@
         <v>31</v>
       </c>
       <c r="O23" s="15">
-        <f>(M23+N23)/2</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="P23" s="15">
-        <f>N23-O23</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q23" s="9" t="s">
@@ -9283,11 +9283,11 @@
         <v>39</v>
       </c>
       <c r="T23" s="15">
-        <f>S23-R23</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="U23" s="15">
-        <f>(R23+S23)/2</f>
+        <f t="shared" si="4"/>
         <v>36.5</v>
       </c>
       <c r="Z23" s="9" t="s">
@@ -9437,7 +9437,7 @@
         <v>1123</v>
       </c>
       <c r="D24" s="12" t="str">
-        <f>CONCATENATE(A24," ",C24)</f>
+        <f t="shared" si="0"/>
         <v>401 竹城甲子園</v>
       </c>
       <c r="E24" s="12" t="s">
@@ -9469,11 +9469,11 @@
         <v>28</v>
       </c>
       <c r="O24" s="15">
-        <f>(M24+N24)/2</f>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="P24" s="15">
-        <f>N24-O24</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q24" s="9" t="s">
@@ -9486,11 +9486,11 @@
         <v>41</v>
       </c>
       <c r="T24" s="15">
-        <f>S24-R24</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="U24" s="15">
-        <f>(R24+S24)/2</f>
+        <f t="shared" si="4"/>
         <v>39.5</v>
       </c>
       <c r="W24" s="9" t="s">
@@ -9640,7 +9640,7 @@
         <v>1142</v>
       </c>
       <c r="D25" s="12" t="str">
-        <f>CONCATENATE(A25," ",C25)</f>
+        <f t="shared" si="0"/>
         <v>501 新未來1</v>
       </c>
       <c r="E25" s="12" t="s">
@@ -9672,11 +9672,11 @@
         <v>38</v>
       </c>
       <c r="O25" s="15">
-        <f>(M25+N25)/2</f>
+        <f t="shared" si="5"/>
         <v>35.5</v>
       </c>
       <c r="P25" s="15">
-        <f>N25-O25</f>
+        <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
       <c r="Q25" s="9" t="s">
@@ -9689,11 +9689,11 @@
         <v>38</v>
       </c>
       <c r="T25" s="15">
-        <f>S25-R25</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="U25" s="15">
-        <f>(R25+S25)/2</f>
+        <f t="shared" si="4"/>
         <v>35.5</v>
       </c>
       <c r="V25" s="15" t="s">
@@ -9846,7 +9846,7 @@
         <v>105</v>
       </c>
       <c r="D26" s="12" t="str">
-        <f t="shared" ref="D26:D33" si="0">CONCATENATE(A26," ",C26)</f>
+        <f t="shared" ref="D26:D33" si="8">CONCATENATE(A26," ",C26)</f>
         <v>102 鴻典</v>
       </c>
       <c r="E26" s="12" t="s">
@@ -9880,11 +9880,11 @@
         <v>26</v>
       </c>
       <c r="O26" s="15">
-        <f t="shared" ref="O26:O47" si="1">(M26+N26)/2</f>
+        <f t="shared" ref="O26:O47" si="9">(M26+N26)/2</f>
         <v>26</v>
       </c>
       <c r="P26" s="15">
-        <f t="shared" ref="P26:P47" si="2">N26-O26</f>
+        <f t="shared" ref="P26:P47" si="10">N26-O26</f>
         <v>0</v>
       </c>
       <c r="Q26" s="9" t="s">
@@ -9897,11 +9897,11 @@
         <v>29</v>
       </c>
       <c r="T26" s="15">
-        <f t="shared" ref="T26:T47" si="3">S26-R26</f>
+        <f t="shared" ref="T26:T47" si="11">S26-R26</f>
         <v>0</v>
       </c>
       <c r="U26" s="15">
-        <f t="shared" ref="U26:U33" si="4">(R26+S26)/2</f>
+        <f t="shared" ref="U26:U33" si="12">(R26+S26)/2</f>
         <v>29</v>
       </c>
       <c r="Z26" s="9" t="s">
@@ -10054,7 +10054,7 @@
         <v>138</v>
       </c>
       <c r="D27" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>105 樂田田</v>
       </c>
       <c r="E27" s="9" t="s">
@@ -10088,11 +10088,11 @@
         <v>26</v>
       </c>
       <c r="O27" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>25.5</v>
       </c>
       <c r="P27" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>0.5</v>
       </c>
       <c r="Q27" s="9" t="s">
@@ -10105,11 +10105,11 @@
         <v>26</v>
       </c>
       <c r="T27" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="U27" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>26</v>
       </c>
       <c r="V27" s="15" t="s">
@@ -10265,7 +10265,7 @@
         <v>362</v>
       </c>
       <c r="D28" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>307 富宇悅峰</v>
       </c>
       <c r="E28" s="12" t="s">
@@ -10299,11 +10299,11 @@
         <v>32</v>
       </c>
       <c r="O28" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
       <c r="P28" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="Q28" s="9" t="s">
@@ -10316,11 +10316,11 @@
         <v>36</v>
       </c>
       <c r="T28" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="U28" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>35</v>
       </c>
       <c r="Z28" s="9" t="s">
@@ -10473,7 +10473,7 @@
         <v>486</v>
       </c>
       <c r="D29" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>408 頤昌豐岳</v>
       </c>
       <c r="E29" s="12" t="s">
@@ -10507,11 +10507,11 @@
         <v>30</v>
       </c>
       <c r="O29" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
       <c r="P29" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Q29" s="9" t="s">
@@ -10524,11 +10524,11 @@
         <v>30</v>
       </c>
       <c r="T29" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="U29" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
       <c r="Z29" s="9" t="s">
@@ -10681,7 +10681,7 @@
         <v>537</v>
       </c>
       <c r="D30" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>411 和洲金剛</v>
       </c>
       <c r="E30" s="12" t="s">
@@ -10715,11 +10715,11 @@
         <v>27</v>
       </c>
       <c r="O30" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>26</v>
       </c>
       <c r="P30" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="Q30" s="9" t="s">
@@ -10732,11 +10732,11 @@
         <v>32</v>
       </c>
       <c r="T30" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="U30" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="Z30" s="9" t="s">
@@ -10883,7 +10883,7 @@
         <v>274</v>
       </c>
       <c r="D31" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>207 和耀恆美</v>
       </c>
       <c r="E31" s="23" t="s">
@@ -10917,11 +10917,11 @@
         <v>33</v>
       </c>
       <c r="O31" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>30.5</v>
       </c>
       <c r="P31" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>2.5</v>
       </c>
       <c r="Q31" s="9" t="s">
@@ -10934,11 +10934,11 @@
         <v>40</v>
       </c>
       <c r="T31" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="U31" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>37.5</v>
       </c>
       <c r="Z31" s="9" t="s">
@@ -11082,7 +11082,7 @@
         <v>505</v>
       </c>
       <c r="D32" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>409 新未來2</v>
       </c>
       <c r="E32" s="12" t="s">
@@ -11116,11 +11116,11 @@
         <v>32</v>
       </c>
       <c r="O32" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>31</v>
       </c>
       <c r="P32" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="Q32" s="9" t="s">
@@ -11133,11 +11133,11 @@
         <v>32</v>
       </c>
       <c r="T32" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="U32" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="Z32" s="9" t="s">
@@ -11290,7 +11290,7 @@
         <v>555</v>
       </c>
       <c r="D33" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v>412 君邑丘比特</v>
       </c>
       <c r="E33" s="12" t="s">
@@ -11324,11 +11324,11 @@
         <v>32</v>
       </c>
       <c r="O33" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>29.9</v>
       </c>
       <c r="P33" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>2.1000000000000014</v>
       </c>
       <c r="Q33" s="9" t="s">
@@ -11341,11 +11341,11 @@
         <v>38.200000000000003</v>
       </c>
       <c r="T33" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>8.4000000000000021</v>
       </c>
       <c r="U33" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>34</v>
       </c>
       <c r="Z33" s="9" t="s">
@@ -11498,7 +11498,7 @@
         <v>597</v>
       </c>
       <c r="D34" s="12" t="str">
-        <f t="shared" ref="D34:D56" si="5">CONCATENATE(A34," ",C34)</f>
+        <f t="shared" ref="D34:D56" si="13">CONCATENATE(A34," ",C34)</f>
         <v>414 合謙學</v>
       </c>
       <c r="E34" s="12" t="s">
@@ -11523,11 +11523,11 @@
         <v>35</v>
       </c>
       <c r="O34" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>33.5</v>
       </c>
       <c r="P34" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>1.5</v>
       </c>
       <c r="Q34" s="9" t="s">
@@ -11540,11 +11540,11 @@
         <v>42</v>
       </c>
       <c r="T34" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
       <c r="U34" s="15">
-        <f t="shared" ref="U34:U54" si="6">(R34+S34)/2</f>
+        <f t="shared" ref="U34:U54" si="14">(R34+S34)/2</f>
         <v>38.5</v>
       </c>
       <c r="Z34" s="9" t="s">
@@ -11676,7 +11676,7 @@
         <v>579</v>
       </c>
       <c r="D35" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>413 頤昌璞岳</v>
       </c>
       <c r="E35" s="12" t="s">
@@ -11710,11 +11710,11 @@
         <v>33</v>
       </c>
       <c r="O35" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>32.5</v>
       </c>
       <c r="P35" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>0.5</v>
       </c>
       <c r="Q35" s="9" t="s">
@@ -11727,11 +11727,11 @@
         <v>33</v>
       </c>
       <c r="T35" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="U35" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>32.5</v>
       </c>
       <c r="Z35" s="9" t="s">
@@ -11878,7 +11878,7 @@
         <v>69</v>
       </c>
       <c r="D36" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>101 和發大境</v>
       </c>
       <c r="E36" s="9" t="s">
@@ -11912,11 +11912,11 @@
         <v>29</v>
       </c>
       <c r="O36" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>28.5</v>
       </c>
       <c r="P36" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>0.5</v>
       </c>
       <c r="Q36" s="9" t="s">
@@ -11929,11 +11929,11 @@
         <v>36</v>
       </c>
       <c r="T36" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="U36" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>35</v>
       </c>
       <c r="Z36" s="9" t="s">
@@ -12086,7 +12086,7 @@
         <v>342</v>
       </c>
       <c r="D37" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>306 華悅城</v>
       </c>
       <c r="E37" s="12" t="s">
@@ -12120,11 +12120,11 @@
         <v>30</v>
       </c>
       <c r="O37" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>28</v>
       </c>
       <c r="P37" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="Q37" s="9" t="s">
@@ -12137,11 +12137,11 @@
         <v>30</v>
       </c>
       <c r="T37" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="U37" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>28</v>
       </c>
       <c r="Z37" s="9" t="s">
@@ -12294,7 +12294,7 @@
         <v>449</v>
       </c>
       <c r="D38" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>405 新A7</v>
       </c>
       <c r="E38" s="12" t="s">
@@ -12328,11 +12328,11 @@
         <v>33</v>
       </c>
       <c r="O38" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>32</v>
       </c>
       <c r="P38" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="Q38" s="9" t="s">
@@ -12345,11 +12345,11 @@
         <v>35</v>
       </c>
       <c r="T38" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="U38" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>33.5</v>
       </c>
       <c r="Z38" s="9" t="s">
@@ -12502,7 +12502,7 @@
         <v>693</v>
       </c>
       <c r="D39" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>505 櫻花澍</v>
       </c>
       <c r="E39" s="12" t="s">
@@ -12536,11 +12536,11 @@
         <v>32</v>
       </c>
       <c r="O39" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
       <c r="P39" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="Q39" s="9" t="s">
@@ -12553,11 +12553,11 @@
         <v>32</v>
       </c>
       <c r="T39" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="U39" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="V39" s="15" t="s">
@@ -12716,7 +12716,7 @@
         <v>248</v>
       </c>
       <c r="D40" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>206 玄泰V1</v>
       </c>
       <c r="E40" s="23" t="s">
@@ -12750,11 +12750,11 @@
         <v>29</v>
       </c>
       <c r="O40" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>28</v>
       </c>
       <c r="P40" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="Q40" s="9" t="s">
@@ -12767,11 +12767,11 @@
         <v>29</v>
       </c>
       <c r="T40" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="U40" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>28</v>
       </c>
       <c r="V40" s="15" t="s">
@@ -12927,7 +12927,7 @@
         <v>427</v>
       </c>
       <c r="D41" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>404 詠勝市中欣</v>
       </c>
       <c r="E41" s="12" t="s">
@@ -12961,11 +12961,11 @@
         <v>32</v>
       </c>
       <c r="O41" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>29.5</v>
       </c>
       <c r="P41" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>2.5</v>
       </c>
       <c r="Q41" s="9" t="s">
@@ -12978,11 +12978,11 @@
         <v>25</v>
       </c>
       <c r="T41" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="U41" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>24.5</v>
       </c>
       <c r="V41" s="15" t="s">
@@ -13138,7 +13138,7 @@
         <v>672</v>
       </c>
       <c r="D42" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>502 富宇天匯</v>
       </c>
       <c r="E42" s="12" t="s">
@@ -13166,11 +13166,11 @@
         <v>43</v>
       </c>
       <c r="O42" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>41</v>
       </c>
       <c r="P42" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="Q42" s="9" t="s">
@@ -13183,11 +13183,11 @@
         <v>50</v>
       </c>
       <c r="T42" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="U42" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>47.5</v>
       </c>
       <c r="Z42" s="9" t="s">
@@ -13340,7 +13340,7 @@
         <v>319</v>
       </c>
       <c r="D43" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>302 欣時代</v>
       </c>
       <c r="E43" s="12" t="s">
@@ -13374,11 +13374,11 @@
         <v>29</v>
       </c>
       <c r="O43" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>28</v>
       </c>
       <c r="P43" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="Q43" s="9" t="s">
@@ -13391,11 +13391,11 @@
         <v>29</v>
       </c>
       <c r="T43" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="U43" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>28</v>
       </c>
       <c r="V43" s="15" t="s">
@@ -13551,7 +13551,7 @@
         <v>614</v>
       </c>
       <c r="D44" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>313 大亮時代A7</v>
       </c>
       <c r="E44" s="12" t="s">
@@ -13585,11 +13585,11 @@
         <v>36</v>
       </c>
       <c r="O44" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>35.5</v>
       </c>
       <c r="P44" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>0.5</v>
       </c>
       <c r="Q44" s="9" t="s">
@@ -13602,11 +13602,11 @@
         <v>36</v>
       </c>
       <c r="T44" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="U44" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>35.5</v>
       </c>
       <c r="Z44" s="9" t="s">
@@ -13753,7 +13753,7 @@
         <v>471</v>
       </c>
       <c r="D45" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>407 富宇哈佛苑</v>
       </c>
       <c r="E45" s="12" t="s">
@@ -13787,11 +13787,11 @@
         <v>38</v>
       </c>
       <c r="O45" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>35.5</v>
       </c>
       <c r="P45" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>2.5</v>
       </c>
       <c r="Q45" s="9" t="s">
@@ -13804,11 +13804,11 @@
         <v>49</v>
       </c>
       <c r="T45" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="U45" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>46.5</v>
       </c>
       <c r="Z45" s="9" t="s">
@@ -13961,7 +13961,7 @@
         <v>523</v>
       </c>
       <c r="D46" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>410 新未來3</v>
       </c>
       <c r="E46" s="12" t="s">
@@ -13995,11 +13995,11 @@
         <v>38</v>
       </c>
       <c r="O46" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>35.5</v>
       </c>
       <c r="P46" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>2.5</v>
       </c>
       <c r="Q46" s="9" t="s">
@@ -14012,11 +14012,11 @@
         <v>38</v>
       </c>
       <c r="T46" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="U46" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>35.5</v>
       </c>
       <c r="Z46" s="9" t="s">
@@ -14169,7 +14169,7 @@
         <v>387</v>
       </c>
       <c r="D47" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>311 文華天際</v>
       </c>
       <c r="E47" s="12" t="s">
@@ -14203,11 +14203,11 @@
         <v>27</v>
       </c>
       <c r="O47" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="9"/>
         <v>27</v>
       </c>
       <c r="P47" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Q47" s="9" t="s">
@@ -14220,11 +14220,11 @@
         <v>34</v>
       </c>
       <c r="T47" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="U47" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>33</v>
       </c>
       <c r="Z47" s="9" t="s">
@@ -14374,7 +14374,7 @@
         <v>657</v>
       </c>
       <c r="D48" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>417 頤昌澄岳</v>
       </c>
       <c r="E48" s="9" t="s">
@@ -14408,7 +14408,7 @@
         <v>40</v>
       </c>
       <c r="U48" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>39.5</v>
       </c>
       <c r="Z48" s="9" t="s">
@@ -14546,7 +14546,7 @@
         <v>636</v>
       </c>
       <c r="D49" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>416 維特魯威</v>
       </c>
       <c r="E49" s="12" t="s">
@@ -14580,7 +14580,7 @@
         <v>45.5</v>
       </c>
       <c r="U49" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>41.65</v>
       </c>
       <c r="AD49" s="9" t="s">
@@ -14709,7 +14709,7 @@
         <v>189</v>
       </c>
       <c r="D50" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>201 富宇上城</v>
       </c>
       <c r="E50" s="12" t="s">
@@ -14758,7 +14758,7 @@
         <v>5</v>
       </c>
       <c r="U50" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>46.5</v>
       </c>
       <c r="Z50" s="9" t="s">
@@ -14911,7 +14911,7 @@
         <v>216</v>
       </c>
       <c r="D51" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>202 禾悅花園</v>
       </c>
       <c r="E51" s="12" t="s">
@@ -14966,7 +14966,7 @@
         <v>2</v>
       </c>
       <c r="U51" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="Z51" s="9" t="s">
@@ -15119,7 +15119,7 @@
         <v>297</v>
       </c>
       <c r="D52" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>301 允將大作</v>
       </c>
       <c r="E52" s="12" t="s">
@@ -15168,7 +15168,7 @@
         <v>5</v>
       </c>
       <c r="U52" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>40.5</v>
       </c>
       <c r="Z52" s="9" t="s">
@@ -15321,7 +15321,7 @@
         <v>162</v>
       </c>
       <c r="D53" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>108 豐邑氧森</v>
       </c>
       <c r="E53" s="12" t="s">
@@ -15355,7 +15355,7 @@
         <v>41</v>
       </c>
       <c r="U53" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>41</v>
       </c>
       <c r="Z53" s="9" t="s">
@@ -15493,7 +15493,7 @@
         <v>408</v>
       </c>
       <c r="D54" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>403 捷市達</v>
       </c>
       <c r="E54" s="12" t="s">
@@ -15542,7 +15542,7 @@
         <v>3</v>
       </c>
       <c r="U54" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>46.5</v>
       </c>
       <c r="Z54" s="9" t="s">
@@ -15695,7 +15695,7 @@
         <v>713</v>
       </c>
       <c r="D55" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>418 玄泰T1</v>
       </c>
       <c r="E55" s="12" t="s">
@@ -15863,7 +15863,7 @@
         <v>733</v>
       </c>
       <c r="D56" s="12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>314 大亮 泊</v>
       </c>
       <c r="E56" s="12" t="s">

--- a/db/A7XLK-1111-HouseApp4.xlsx
+++ b/db/A7XLK-1111-HouseApp4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F6EC31-0DF0-174C-B6BD-833BB3C0E4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7387413E-47F4-844D-8CF7-39884620A4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-5500" yWindow="-20620" windowWidth="27320" windowHeight="16380" xr2:uid="{33D194D6-A429-7949-A97B-0894189945E2}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2248" uniqueCount="1159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2224" uniqueCount="1158">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -4480,10 +4480,6 @@
   </si>
   <si>
     <t>Category2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>已交屋</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -5323,9 +5319,6 @@
       <c r="AK2" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL2" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM2" s="9" t="s">
         <v>116</v>
       </c>
@@ -5457,9 +5450,6 @@
       <c r="AK3" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL3" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM3" s="9" t="s">
         <v>116</v>
       </c>
@@ -5588,9 +5578,6 @@
       <c r="AK4" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL4" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM4" s="9" t="s">
         <v>116</v>
       </c>
@@ -5719,9 +5706,6 @@
       <c r="AK5" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL5" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM5" s="9" t="s">
         <v>116</v>
       </c>
@@ -5850,9 +5834,6 @@
       <c r="AK6" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL6" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM6" s="9" t="s">
         <v>116</v>
       </c>
@@ -6065,9 +6046,6 @@
       <c r="AK7" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL7" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM7" s="9" t="s">
         <v>814</v>
       </c>
@@ -6272,9 +6250,6 @@
       <c r="AK8" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL8" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM8" s="9" t="s">
         <v>116</v>
       </c>
@@ -6466,9 +6441,6 @@
       <c r="AK9" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL9" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM9" s="9" t="s">
         <v>116</v>
       </c>
@@ -6679,9 +6651,6 @@
       <c r="AK10" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL10" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM10" s="9" t="s">
         <v>116</v>
       </c>
@@ -6888,9 +6857,6 @@
       <c r="AK11" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL11" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM11" s="9" t="s">
         <v>116</v>
       </c>
@@ -7100,9 +7066,6 @@
       <c r="AK12" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL12" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM12" s="9" t="s">
         <v>116</v>
       </c>
@@ -7315,9 +7278,6 @@
       <c r="AK13" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL13" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM13" s="9" t="s">
         <v>116</v>
       </c>
@@ -7527,9 +7487,6 @@
       <c r="AK14" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL14" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM14" s="9" t="s">
         <v>116</v>
       </c>
@@ -7739,9 +7696,6 @@
       <c r="AK15" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL15" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM15" s="9" t="s">
         <v>116</v>
       </c>
@@ -7951,9 +7905,6 @@
       <c r="AK16" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL16" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM16" s="9" t="s">
         <v>116</v>
       </c>
@@ -8118,9 +8069,6 @@
       <c r="AK17" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL17" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM17" s="9" t="s">
         <v>171</v>
       </c>
@@ -8291,9 +8239,6 @@
       <c r="AK18" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL18" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM18" s="9" t="s">
         <v>116</v>
       </c>
@@ -8503,9 +8448,6 @@
       <c r="AK19" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL19" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM19" s="9" t="s">
         <v>116</v>
       </c>
@@ -8712,9 +8654,6 @@
       <c r="AK20" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL20" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM20" s="9" t="s">
         <v>116</v>
       </c>
@@ -8914,9 +8853,6 @@
       <c r="AK21" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL21" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM21" s="9" t="s">
         <v>116</v>
       </c>
@@ -9120,9 +9056,6 @@
       <c r="AK22" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL22" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM22" s="9" t="s">
         <v>116</v>
       </c>
@@ -9326,9 +9259,6 @@
       <c r="AK23" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL23" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM23" s="9" t="s">
         <v>116</v>
       </c>
@@ -9526,9 +9456,6 @@
       <c r="AK24" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL24" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM24" s="9" t="s">
         <v>116</v>
       </c>
@@ -9732,9 +9659,6 @@
       <c r="AK25" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AL25" s="9" t="s">
-        <v>1157</v>
-      </c>
       <c r="AM25" s="9" t="s">
         <v>116</v>
       </c>
@@ -9941,7 +9865,7 @@
         <v>82</v>
       </c>
       <c r="AL26" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM26" s="9" t="s">
         <v>116</v>
@@ -10152,7 +10076,7 @@
         <v>82</v>
       </c>
       <c r="AL27" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM27" s="9" t="s">
         <v>116</v>
@@ -10360,7 +10284,7 @@
         <v>82</v>
       </c>
       <c r="AL28" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM28" s="9" t="s">
         <v>368</v>
@@ -10568,7 +10492,7 @@
         <v>82</v>
       </c>
       <c r="AL29" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM29" s="9" t="s">
         <v>116</v>
@@ -10770,7 +10694,7 @@
         <v>82</v>
       </c>
       <c r="AL30" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM30" s="9" t="s">
         <v>116</v>
@@ -10972,7 +10896,7 @@
         <v>82</v>
       </c>
       <c r="AL31" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM31" s="9" t="s">
         <v>116</v>
@@ -11177,7 +11101,7 @@
         <v>82</v>
       </c>
       <c r="AL32" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM32" s="9" t="s">
         <v>116</v>
@@ -11385,7 +11309,7 @@
         <v>82</v>
       </c>
       <c r="AL33" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM33" s="9" t="s">
         <v>564</v>
@@ -11578,7 +11502,7 @@
         <v>82</v>
       </c>
       <c r="AL34" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM34" s="9" t="s">
         <v>564</v>
@@ -11765,7 +11689,7 @@
         <v>82</v>
       </c>
       <c r="AL35" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM35" s="9" t="s">
         <v>564</v>
@@ -11973,7 +11897,7 @@
         <v>82</v>
       </c>
       <c r="AL36" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM36" s="9" t="s">
         <v>83</v>
@@ -12181,7 +12105,7 @@
         <v>82</v>
       </c>
       <c r="AL37" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM37" s="9" t="s">
         <v>116</v>
@@ -12389,7 +12313,7 @@
         <v>82</v>
       </c>
       <c r="AL38" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM38" s="9" t="s">
         <v>116</v>
@@ -12606,7 +12530,7 @@
         <v>82</v>
       </c>
       <c r="AL39" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM39" s="9" t="s">
         <v>116</v>
@@ -12814,7 +12738,7 @@
         <v>82</v>
       </c>
       <c r="AL40" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM40" s="9" t="s">
         <v>116</v>
@@ -13025,7 +12949,7 @@
         <v>82</v>
       </c>
       <c r="AL41" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM41" s="9" t="s">
         <v>116</v>
@@ -13227,7 +13151,7 @@
         <v>82</v>
       </c>
       <c r="AL42" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM42" s="9" t="s">
         <v>116</v>
@@ -13438,7 +13362,7 @@
         <v>82</v>
       </c>
       <c r="AL43" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM43" s="9" t="s">
         <v>116</v>
@@ -13646,7 +13570,7 @@
         <v>82</v>
       </c>
       <c r="AL44" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM44" s="9" t="s">
         <v>622</v>
@@ -13848,7 +13772,7 @@
         <v>82</v>
       </c>
       <c r="AL45" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM45" s="9" t="s">
         <v>116</v>
@@ -14056,7 +13980,7 @@
         <v>82</v>
       </c>
       <c r="AL46" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM46" s="9" t="s">
         <v>116</v>
@@ -14264,7 +14188,7 @@
         <v>82</v>
       </c>
       <c r="AL47" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM47" s="9" t="s">
         <v>116</v>
@@ -14445,7 +14369,7 @@
         <v>82</v>
       </c>
       <c r="AL48" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM48" s="9" t="s">
         <v>171</v>
@@ -14608,7 +14532,7 @@
         <v>82</v>
       </c>
       <c r="AL49" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM49" s="9" t="s">
         <v>171</v>
@@ -14798,7 +14722,7 @@
         <v>82</v>
       </c>
       <c r="AL50" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM50" s="9" t="s">
         <v>116</v>
@@ -15006,7 +14930,7 @@
         <v>82</v>
       </c>
       <c r="AL51" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM51" s="9" t="s">
         <v>116</v>
@@ -15208,7 +15132,7 @@
         <v>82</v>
       </c>
       <c r="AL52" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM52" s="9" t="s">
         <v>116</v>
@@ -15392,7 +15316,7 @@
         <v>82</v>
       </c>
       <c r="AL53" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM53" s="9" t="s">
         <v>171</v>
@@ -15582,7 +15506,7 @@
         <v>82</v>
       </c>
       <c r="AL54" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM54" s="9" t="s">
         <v>116</v>
@@ -15765,7 +15689,7 @@
         <v>82</v>
       </c>
       <c r="AL55" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM55" s="9" t="s">
         <v>171</v>
@@ -15937,7 +15861,7 @@
         <v>82</v>
       </c>
       <c r="AL56" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AM56" s="9" t="s">
         <v>622</v>
